--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>38.50931677018632</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>28.77697841726621</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>32.88590604026847</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>7.823129251700678</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>21.85430463576159</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -552,13 +552,13 @@
         <v>12.96296296296295</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="C8">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="D8">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="E8">
-        <v>0.2399999999999998</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="F8">
-        <v>8.540925266903908</v>
+        <v>-14.28571428571428</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="D9">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="E9">
-        <v>0.3499999999999999</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="F9">
-        <v>22.0125786163522</v>
+        <v>59.47712418300652</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -621,25 +621,25 @@
         </is>
       </c>
       <c r="C10">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="D10">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="E10">
-        <v>0.3000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="F10">
-        <v>13.95348837209303</v>
+        <v>9.251101321585908</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Antártica Chilena</t>
+          <t>Ultima Esperanza</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="D11">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="E11">
-        <v>-0.4199999999999999</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="F11">
-        <v>-14.28571428571428</v>
+        <v>10.39999999999999</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Antártica Chilena</t>
+          <t>Ultima Esperanza</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="D12">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="E12">
-        <v>0.9099999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="F12">
-        <v>59.47712418300652</v>
+        <v>22.22222222222223</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Antártica Chilena</t>
+          <t>Ultima Esperanza</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -702,99 +702,18 @@
         </is>
       </c>
       <c r="C13">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="D13">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="E13">
-        <v>0.21</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="F13">
-        <v>9.251101321585908</v>
+        <v>16.37168141592922</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ultima Esperanza</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>2.76</v>
-      </c>
-      <c r="D14">
-        <v>2.5</v>
-      </c>
-      <c r="E14">
-        <v>0.2599999999999998</v>
-      </c>
-      <c r="F14">
-        <v>10.39999999999999</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ultima Esperanza</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>2.53</v>
-      </c>
-      <c r="D15">
-        <v>2.07</v>
-      </c>
-      <c r="E15">
-        <v>0.46</v>
-      </c>
-      <c r="F15">
-        <v>22.22222222222223</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ultima Esperanza</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>2.63</v>
-      </c>
-      <c r="D16">
-        <v>2.26</v>
-      </c>
-      <c r="E16">
-        <v>0.3700000000000001</v>
-      </c>
-      <c r="F16">
-        <v>16.37168141592922</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -867,7 +786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1108,60 +1027,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>2.9</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>2.15</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>2.45</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Antártica Chilena</t>
   </si>
   <si>
-    <t xml:space="preserve">Ultima Esperanza</t>
+    <t xml:space="preserve">Última Esperanza</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:19</t>
+    <t xml:space="preserve">2026-08-19 15:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -83,13 +83,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringrmin_a_2024_magallanes.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -833,23 +839,23 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -929,10 +935,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -940,7 +946,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>3.26</v>
@@ -951,7 +957,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2.27</v>
@@ -962,7 +968,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>2.48</v>
@@ -973,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>2.87</v>
@@ -984,7 +990,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>2.16</v>
@@ -995,7 +1001,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>2.44</v>
@@ -1006,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>2.11</v>
@@ -1017,7 +1023,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1.49</v>
@@ -1028,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1.98</v>
@@ -1039,7 +1045,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>3.3</v>
@@ -1050,7 +1056,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>2.26</v>
@@ -1061,7 +1067,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>2.63</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_magallanes.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:21</t>
+    <t xml:space="preserve">2026-09-07 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
